--- a/data/trans_bre/P34A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P34A_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 2,16</t>
+          <t>-8,83; 1,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 8,97</t>
+          <t>-0,94; 8,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 16,25</t>
+          <t>5,54; 15,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 5,04</t>
+          <t>-5,65; 4,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 5,04</t>
+          <t>-18,28; 4,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 42,4</t>
+          <t>-3,24; 40,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,7; 48,87</t>
+          <t>14,21; 48,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 14,49</t>
+          <t>-13,45; 13,37</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 9,35</t>
+          <t>0,51; 9,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,09; 16,75</t>
+          <t>8,2; 16,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 12,39</t>
+          <t>3,68; 12,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 24,06</t>
+          <t>3,97; 27,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 23,79</t>
+          <t>0,99; 24,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,82; 75,95</t>
+          <t>31,05; 74,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,59; 38,02</t>
+          <t>10,07; 38,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,15; 165,16</t>
+          <t>11,49; 179,16</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 11,17</t>
+          <t>1,35; 11,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 11,95</t>
+          <t>2,72; 11,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 11,34</t>
+          <t>1,72; 11,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 15,76</t>
+          <t>-16,06; 16,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 37,31</t>
+          <t>3,67; 39,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,13; 65,2</t>
+          <t>11,76; 63,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 36,56</t>
+          <t>4,71; 36,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-45,51; 48,35</t>
+          <t>-45,78; 48,31</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 14,21</t>
+          <t>5,86; 14,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 12,34</t>
+          <t>4,59; 12,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,57; 15,01</t>
+          <t>6,44; 15,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 13,55</t>
+          <t>1,5; 13,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,19; 34,78</t>
+          <t>12,48; 34,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,5; 64,28</t>
+          <t>19,48; 64,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,81; 50,41</t>
+          <t>18,58; 49,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 49,42</t>
+          <t>5,74; 51,08</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,49</t>
+          <t>2,65; 7,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,55</t>
+          <t>6,21; 10,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 11,18</t>
+          <t>6,51; 11,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 14,16</t>
+          <t>0,84; 13,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 18,72</t>
+          <t>6,23; 18,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,35; 49,77</t>
+          <t>26,13; 50,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,7; 34,37</t>
+          <t>18,62; 35,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 54,42</t>
+          <t>3,31; 52,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P34A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P34A_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>-0,52</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-0,53%</t>
+          <t>-1,33%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 1,66</t>
+          <t>-9,25; 1,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 8,43</t>
+          <t>-0,59; 8,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,54; 15,64</t>
+          <t>5,64; 15,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 4,77</t>
+          <t>-5,45; 4,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 4,09</t>
+          <t>-18,92; 4,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 40,65</t>
+          <t>-2,2; 42,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,21; 48,23</t>
+          <t>13,42; 49,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 13,37</t>
+          <t>-12,67; 12,96</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,13</t>
+          <t>5,22</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 9,64</t>
+          <t>0,12; 9,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,2; 16,55</t>
+          <t>8,11; 16,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 12,48</t>
+          <t>3,22; 12,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 27,21</t>
+          <t>0,8; 9,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 24,57</t>
+          <t>0,3; 24,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,05; 74,4</t>
+          <t>30,42; 76,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,07; 38,13</t>
+          <t>8,62; 36,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,49; 179,16</t>
+          <t>2,19; 30,28</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>9,85</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 11,7</t>
+          <t>1,64; 11,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 11,87</t>
+          <t>2,78; 12,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 11,48</t>
+          <t>1,82; 11,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 16,02</t>
+          <t>4,73; 14,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,67; 39,43</t>
+          <t>4,59; 39,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,76; 63,02</t>
+          <t>11,87; 65,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 36,86</t>
+          <t>5,35; 39,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-45,78; 48,31</t>
+          <t>12,34; 44,5</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,7</t>
+          <t>12,07</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>42,43%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 14,23</t>
+          <t>5,18; 14,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 12,42</t>
+          <t>4,97; 12,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 15,13</t>
+          <t>6,38; 15,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 13,71</t>
+          <t>8,11; 15,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,48; 34,83</t>
+          <t>11,18; 34,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,48; 64,27</t>
+          <t>21,0; 66,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,58; 49,39</t>
+          <t>18,9; 50,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,74; 51,08</t>
+          <t>25,87; 60,94</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>7,05</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,45</t>
+          <t>2,44; 7,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,21; 10,68</t>
+          <t>6,25; 10,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,37</t>
+          <t>6,48; 11,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 13,63</t>
+          <t>4,98; 9,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 18,6</t>
+          <t>5,71; 18,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,13; 50,2</t>
+          <t>26,67; 49,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,62; 35,42</t>
+          <t>18,58; 34,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 52,15</t>
+          <t>14,15; 29,71</t>
         </is>
       </c>
     </row>
